--- a/etf_holdings/2026-10-20_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-20_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:40</t>
+          <t>2026-10-20 21:42:31</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,25 +509,25 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0%2420</t>
+          <t>-0.62%2405</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-0.62%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2420</v>
+        <v>2405</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>12.77%1,680,000</t>
+          <t>13.78%1,680,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>12.77%</t>
+          <t>13.78%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:40</t>
+          <t>2026-10-20 21:42:31</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -565,38 +565,38 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1216統一</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0%79.6</t>
+          <t>+1.37%6650</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.37%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>79.59999999999999</v>
+        <v>6650</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>3.61%14,442,000</t>
+          <t>3.25%146,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3.61%</t>
+          <t>3.25%</t>
         </is>
       </c>
       <c r="K3" t="n">
-        <v>14442000</v>
+        <v>146000</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:40</t>
+          <t>2026-10-20 21:42:31</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -626,38 +626,38 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>4904遠傳</t>
+          <t>1216統一</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.88%112.5</t>
+          <t>-1.51%78.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>-1.51%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>112.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3.26%9,139,000</t>
+          <t>3.16%11,728,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>3.26%</t>
+          <t>3.16%</t>
         </is>
       </c>
       <c r="K4" t="n">
-        <v>9139000</v>
+        <v>11728000</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:40</t>
+          <t>2026-10-20 21:42:31</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -687,38 +687,38 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>7769鴻勁</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-2.53%6560</t>
+          <t>-3.61%5205</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-2.53%</t>
+          <t>-3.61%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>6560</v>
+        <v>5205</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3.09%146,000</t>
+          <t>3.07%168,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>3.07%</t>
         </is>
       </c>
       <c r="K5" t="n">
-        <v>146000</v>
+        <v>168000</v>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:40</t>
+          <t>2026-10-20 21:42:31</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>7769鴻勁</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>+2.18%5400</t>
+          <t>-3.51%4945</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>+2.18%</t>
+          <t>-3.51%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>5400</v>
+        <v>4945</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.66%160,000</t>
+          <t>2.87%165,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2.66%</t>
+          <t>2.87%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>160000</v>
+        <v>165000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>-0.10%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:40</t>
+          <t>2026-10-20 21:42:31</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.77%5125</t>
+          <t>-1.75%1970</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-0.77%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>5125</v>
+        <v>1970</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.65%163,000</t>
+          <t>2.74%403,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2.65%</t>
+          <t>2.74%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>163000</v>
+        <v>403000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:40</t>
+          <t>2026-10-20 21:42:31</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3036文曄</t>
+          <t>4904遠傳</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-2.14%205.5</t>
+          <t>-0.44%112</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-2.14%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>205.5</v>
+        <v>112</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.41%3,650,000</t>
+          <t>2.74%7,183,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.74%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>3650000</v>
+        <v>7183000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:40</t>
+          <t>2026-10-20 21:42:31</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+1.26%2005</t>
+          <t>-2.13%1605</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+1.26%</t>
+          <t>-2.13%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>2005</v>
+        <v>1605</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.35%378,000</t>
+          <t>2.57%462,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.57%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>378000</v>
+        <v>462000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:40</t>
+          <t>2026-10-20 21:42:31</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6446藥華藥</t>
+          <t>3036文曄</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-5.62%1175</t>
+          <t>+0.97%207.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-5.62%</t>
+          <t>+0.97%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1175</v>
+        <v>207.5</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.15%550,000</t>
+          <t>2.54%3,650,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>2.54%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>550000</v>
+        <v>3650000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:40</t>
+          <t>2026-10-20 21:42:31</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>6669緯穎</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.35%9920</t>
+          <t>+2.12%1925</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.35%</t>
+          <t>+2.12%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>9920</v>
+        <v>1925</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.13%68,000</t>
+          <t>2.50%392,036</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2.13%</t>
+          <t>2.50%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>68000</v>
+        <v>392036</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:40</t>
+          <t>2026-10-20 21:42:31</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2376技嘉</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-1.54%352</t>
+          <t>+1.81%10100</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-1.54%</t>
+          <t>+1.81%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>352</v>
+        <v>10100</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.99%1,769,000</t>
+          <t>2.29%68,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.99%</t>
+          <t>2.29%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>1769000</v>
+        <v>68000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:40</t>
+          <t>2026-10-20 21:42:31</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>6446藥華藥</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+2.75%1120</t>
+          <t>-1.7%1155</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+2.75%</t>
+          <t>-1.7%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1120</v>
+        <v>1155</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1.90%555,000</t>
+          <t>2.19%550,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>1.90%</t>
+          <t>2.19%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>555000</v>
+        <v>550000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:40</t>
+          <t>2026-10-20 21:42:31</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3081聯亞</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+0.98%2570</t>
+          <t>-5.8%1055</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+0.98%</t>
+          <t>-5.8%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>2570</v>
+        <v>1055</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1.89%236,000</t>
+          <t>2.11%555,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1.89%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>236000</v>
+        <v>555000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.13%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:40</t>
+          <t>2026-10-20 21:42:31</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>2376技嘉</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+0.31%1640</t>
+          <t>+0.85%355</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>+0.85%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1640</v>
+        <v>355</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1.75%340,000</t>
+          <t>2.11%1,769,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>2.11%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>340000</v>
+        <v>1769000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:40</t>
+          <t>2026-10-20 21:42:31</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2027大成鋼</t>
+          <t>3081聯亞</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+0.2%51</t>
+          <t>-3.11%2490</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+0.2%</t>
+          <t>-3.11%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>51</v>
+        <v>2490</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1.74%10,874,000</t>
+          <t>1.98%227,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1.74%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>10874000</v>
+        <v>227000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:41</t>
+          <t>2026-10-20 21:42:33</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2603長榮</t>
+          <t>2027大成鋼</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-1.32%262</t>
+          <t>-2.06%49.95</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-1.32%</t>
+          <t>-2.06%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>262</v>
+        <v>49.95</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.72%2,059,000</t>
+          <t>1.88%10,874,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.88%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>2059000</v>
+        <v>10874000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:41</t>
+          <t>2026-10-20 21:42:33</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2609陽明</t>
+          <t>2603長榮</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-1.85%63.5</t>
+          <t>-0.95%259.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-1.85%</t>
+          <t>-0.95%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>63.5</v>
+        <v>259.5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.71%8,425,000</t>
+          <t>1.83%2,059,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.71%</t>
+          <t>1.83%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>8425000</v>
+        <v>2059000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:41</t>
+          <t>2026-10-20 21:42:33</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,34 +1541,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>2609陽明</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-2.42%6245</t>
+          <t>-2.05%62.2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-2.42%</t>
+          <t>-2.05%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>6245</v>
+        <v>62.2</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.69%84,000</t>
+          <t>1.81%8,425,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>84000</v>
+        <v>8425000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:41</t>
+          <t>2026-10-20 21:42:33</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,34 +1602,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2408南亞科</t>
+          <t>2327國巨*</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-2.57%436</t>
+          <t>-2.06%523</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-2.57%</t>
+          <t>-2.06%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>436</v>
+        <v>523</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.54%1,092,000</t>
+          <t>1.81%999,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.81%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1092000</v>
+        <v>999000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:41</t>
+          <t>2026-10-20 21:42:33</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2610華航</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-2.38%20.55</t>
+          <t>-4.32%5975</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-2.38%</t>
+          <t>-4.32%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>20.55</v>
+        <v>5975</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.54%23,341,000</t>
+          <t>1.78%84,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.78%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>23341000</v>
+        <v>84000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:41</t>
+          <t>2026-10-20 21:42:33</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+0.15%3320</t>
+          <t>+0.15%3325</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1738,16 +1738,16 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>3320</v>
+        <v>3325</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.51%145,000</t>
+          <t>1.63%145,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.51%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:41</t>
+          <t>2026-10-20 21:42:33</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>2610華航</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-0.15%670</t>
+          <t>-0.73%20.4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>-0.73%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>670</v>
+        <v>20.4</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.48%704,000</t>
+          <t>1.63%23,341,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.48%</t>
+          <t>1.63%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>704000</v>
+        <v>23341000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:41</t>
+          <t>2026-10-20 21:42:33</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1402遠東新</t>
+          <t>2408南亞科</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-1.87%28.85</t>
+          <t>-3.21%422</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-1.87%</t>
+          <t>-3.21%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>28.85</v>
+        <v>422</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.47%15,953,000</t>
+          <t>1.61%1,092,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.61%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>15953000</v>
+        <v>1092000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:41</t>
+          <t>2026-10-20 21:42:33</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>6488環球晶</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-2.22%882</t>
+          <t>-1.49%660</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-2.22%</t>
+          <t>-1.49%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>882</v>
+        <v>660</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.39%492,000</t>
+          <t>1.60%704,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.60%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>492000</v>
+        <v>704000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:41</t>
+          <t>2026-10-20 21:42:33</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2327國巨*</t>
+          <t>1402遠東新</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-5.82%534</t>
+          <t>-1.21%28.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-5.82%</t>
+          <t>-1.21%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>534</v>
+        <v>28.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.37%770,000</t>
+          <t>1.56%15,953,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.56%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>770000</v>
+        <v>15953000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:41</t>
+          <t>2026-10-20 21:42:33</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2454聯發科</t>
+          <t>2412中華電</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-1.06%4205</t>
+          <t>0%154.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-1.06%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>4205</v>
+        <v>154.5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.36%102,000</t>
+          <t>1.48%2,818,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.36%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>102000</v>
+        <v>2818000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:41</t>
+          <t>2026-10-20 21:42:33</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2412中華電</t>
+          <t>6488環球晶</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+0.98%154.5</t>
+          <t>-4.31%844</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+0.98%</t>
+          <t>-4.31%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>154.5</v>
+        <v>844</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.35%2,818,000</t>
+          <t>1.47%492,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>2818000</v>
+        <v>492000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:41</t>
+          <t>2026-10-20 21:42:33</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2454聯發科</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-1.99%1975</t>
+          <t>-1.31%4150</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-1.99%</t>
+          <t>-1.31%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>1975</v>
+        <v>4150</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.34%211,000</t>
+          <t>1.45%102,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.34%</t>
+          <t>1.45%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>211000</v>
+        <v>102000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:41</t>
+          <t>2026-10-20 21:42:33</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1605華新</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-2.47%37.55</t>
+          <t>-2.53%1925</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-2.47%</t>
+          <t>-2.53%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>37.55</v>
+        <v>1925</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.33%10,998,000</t>
+          <t>1.41%211,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.41%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>10998000</v>
+        <v>211000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:41</t>
+          <t>2026-10-20 21:42:33</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>6669緯穎</t>
+          <t>1605華新</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+2.17%1885</t>
+          <t>-1.46%37</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+2.17%</t>
+          <t>-1.46%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>1885</v>
+        <v>37</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.32%227,036</t>
+          <t>1.40%10,998,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.40%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>227036</v>
+        <v>10998000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:42</t>
+          <t>2026-10-20 21:42:34</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,25 +2339,25 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-1.13%131.5</t>
+          <t>-3.42%127</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1.13%</t>
+          <t>-3.42%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>131.5</v>
+        <v>127</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.30%3,110,000</t>
+          <t>1.39%3,110,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.30%</t>
+          <t>1.39%</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:42</t>
+          <t>2026-10-20 21:42:34</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,25 +2400,25 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-0.55%27.15</t>
+          <t>-1.29%26.8</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>-1.29%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>27.15</v>
+        <v>26.8</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.24%14,486,000</t>
+          <t>1.33%14,486,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.24%</t>
+          <t>1.33%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:42</t>
+          <t>2026-10-20 21:42:34</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,25 +2461,25 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+0.4%1250</t>
+          <t>-5.2%1185</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+0.4%</t>
+          <t>-5.2%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1250</v>
+        <v>1185</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.22%311,000</t>
+          <t>1.32%311,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.32%</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:42</t>
+          <t>2026-10-20 21:42:34</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,25 +2522,25 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-1.84%239.5</t>
+          <t>+0.84%241.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-1.84%</t>
+          <t>+0.84%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>239.5</v>
+        <v>241.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>1.21%1,579,000</t>
+          <t>1.28%1,579,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.28%</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:42</t>
+          <t>2026-10-20 21:42:34</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2578,38 +2578,38 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>6531愛普*</t>
+          <t>2344華邦電</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-6.92%821</t>
+          <t>-1.93%152.5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-6.92%</t>
+          <t>-1.93%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>821</v>
+        <v>152.5</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.08%389,000</t>
+          <t>1.21%2,294,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="K36" t="n">
-        <v>389000</v>
+        <v>2294000</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:42</t>
+          <t>2026-10-20 21:42:34</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,25 +2644,25 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-3.79%482</t>
+          <t>-1.45%475</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-3.79%</t>
+          <t>-1.45%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>482</v>
+        <v>475</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.05%666,000</t>
+          <t>1.09%666,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.05%</t>
+          <t>1.09%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:42</t>
+          <t>2026-10-20 21:42:34</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>6442光聖</t>
+          <t>6531愛普*</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-0.66%1495</t>
+          <t>-2.56%800</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-0.66%</t>
+          <t>-2.56%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>1495</v>
+        <v>800</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.95%201,000</t>
+          <t>1.08%389,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>1.08%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>201000</v>
+        <v>389000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:42</t>
+          <t>2026-10-20 21:42:34</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2377微星</t>
+          <t>6442光聖</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-1.24%159.5</t>
+          <t>-2.68%1455</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-1.24%</t>
+          <t>-2.68%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>159.5</v>
+        <v>1455</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.80%1,576,000</t>
+          <t>1.02%201,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.80%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>1576000</v>
+        <v>201000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:42</t>
+          <t>2026-10-20 21:42:34</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>3661世芯-KY</t>
+          <t>2377微星</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+0.81%3715</t>
+          <t>+3.13%164.5</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+0.81%</t>
+          <t>+3.13%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>3715</v>
+        <v>164.5</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.59%51,000</t>
+          <t>0.85%1,576,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.59%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>51000</v>
+        <v>1576000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:42</t>
+          <t>2026-10-20 21:42:34</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,38 +2883,38 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>7750新代</t>
+          <t>3661世芯-KY</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-0.55%1820</t>
+          <t>-2.02%3640</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>-2.02%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>1820</v>
+        <v>3640</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.56%97,000</t>
+          <t>0.64%51,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.56%</t>
+          <t>0.64%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>97000</v>
+        <v>51000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:42</t>
+          <t>2026-10-20 21:42:34</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1504東元</t>
+          <t>7750新代</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-0.57%69.3</t>
+          <t>+0.27%1825</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-0.57%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>69.3</v>
+        <v>1825</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.48%2,177,000</t>
+          <t>0.60%97,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>2177000</v>
+        <v>97000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:42</t>
+          <t>2026-10-20 21:42:34</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1301台塑</t>
+          <t>1504東元</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-4.75%78.2</t>
+          <t>-1.44%68.3</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-4.75%</t>
+          <t>-1.44%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>78.2</v>
+        <v>68.3</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.44%1,724,000</t>
+          <t>0.51%2,177,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.51%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>1724000</v>
+        <v>2177000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:42</t>
+          <t>2026-10-20 21:42:34</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>6526達發</t>
+          <t>3189景碩</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-0.26%781</t>
+          <t>-3.77%945</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-0.26%</t>
+          <t>-3.77%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>781</v>
+        <v>945</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.25%102,000</t>
+          <t>0.50%149,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.25%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>102000</v>
+        <v>149000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:42</t>
+          <t>2026-10-20 21:42:34</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,38 +3127,38 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>3491昇達科</t>
+          <t>1301台塑</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-4.81%1385</t>
+          <t>-4.22%74.9</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-4.81%</t>
+          <t>-4.22%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1385</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.18%40,000</t>
+          <t>0.46%1,724,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.18%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>40000</v>
+        <v>1724000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:42</t>
+          <t>2026-10-20 21:42:34</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,38 +3188,38 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2344華邦電</t>
+          <t>6526達發</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-3.72%155.5</t>
+          <t>+2.56%801</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-3.72%</t>
+          <t>+2.56%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>155.5</v>
+        <v>801</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.08%156,000</t>
+          <t>0.27%102,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.08%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>156000</v>
+        <v>102000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:44</t>
+          <t>2026-10-20 21:42:35</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,38 +3249,38 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2881富邦金</t>
+          <t>3491昇達科</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-1.86%158.5</t>
+          <t>-3.97%1330</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-1.86%</t>
+          <t>-3.97%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>158.5</v>
+        <v>1330</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0.01%17,000</t>
+          <t>0.19%40,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>0.19%</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>17000</v>
+        <v>40000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:44</t>
+          <t>2026-10-20 21:42:35</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,25 +3310,25 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>2881富邦金</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+1.85%1380</t>
+          <t>-3.15%153.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+1.85%</t>
+          <t>-3.15%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>1380</v>
+        <v>153.5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.01%2,000</t>
+          <t>0.01%17,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3337,11 +3337,11 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>2000</v>
+        <v>17000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:44</t>
+          <t>2026-10-20 21:42:35</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,38 +3371,38 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-2.87%1525</t>
+          <t>-5.43%1305</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-2.87%</t>
+          <t>-5.43%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1525</v>
+        <v>1305</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0.01%2,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="K49" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:44</t>
+          <t>2026-10-20 21:42:35</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,30 +3432,30 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2395研華</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-0.88%679</t>
+          <t>+1.31%1545</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-0.88%</t>
+          <t>+1.31%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>679</v>
+        <v>1545</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0.01%1,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="K50" t="n">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-20 00:29:44</t>
+          <t>2026-10-20 21:42:35</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3493,21 +3493,21 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>3189景碩</t>
+          <t>2395研華</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-1.8%982</t>
+          <t>+0.74%684</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>+0.74%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>982</v>
+        <v>684</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>

--- a/etf_holdings/2026-10-20_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-20_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:31</t>
+          <t>2026-10-20 21:53:22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:31</t>
+          <t>2026-10-20 21:53:22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:31</t>
+          <t>2026-10-20 21:53:22</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:31</t>
+          <t>2026-10-20 21:53:22</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:31</t>
+          <t>2026-10-20 21:53:22</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:31</t>
+          <t>2026-10-20 21:53:22</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:31</t>
+          <t>2026-10-20 21:53:22</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:31</t>
+          <t>2026-10-20 21:53:22</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:31</t>
+          <t>2026-10-20 21:53:22</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:31</t>
+          <t>2026-10-20 21:53:22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:31</t>
+          <t>2026-10-20 21:53:22</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:31</t>
+          <t>2026-10-20 21:53:22</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:31</t>
+          <t>2026-10-20 21:53:22</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:31</t>
+          <t>2026-10-20 21:53:22</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:31</t>
+          <t>2026-10-20 21:53:22</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:33</t>
+          <t>2026-10-20 21:53:24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:33</t>
+          <t>2026-10-20 21:53:24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:33</t>
+          <t>2026-10-20 21:53:24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:33</t>
+          <t>2026-10-20 21:53:24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:33</t>
+          <t>2026-10-20 21:53:24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:33</t>
+          <t>2026-10-20 21:53:24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:33</t>
+          <t>2026-10-20 21:53:24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:33</t>
+          <t>2026-10-20 21:53:24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:33</t>
+          <t>2026-10-20 21:53:24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:33</t>
+          <t>2026-10-20 21:53:24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:33</t>
+          <t>2026-10-20 21:53:24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:33</t>
+          <t>2026-10-20 21:53:24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:33</t>
+          <t>2026-10-20 21:53:24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:33</t>
+          <t>2026-10-20 21:53:24</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:33</t>
+          <t>2026-10-20 21:53:24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:34</t>
+          <t>2026-10-20 21:53:25</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:34</t>
+          <t>2026-10-20 21:53:25</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:34</t>
+          <t>2026-10-20 21:53:25</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:34</t>
+          <t>2026-10-20 21:53:25</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:34</t>
+          <t>2026-10-20 21:53:25</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:34</t>
+          <t>2026-10-20 21:53:25</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:34</t>
+          <t>2026-10-20 21:53:25</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:34</t>
+          <t>2026-10-20 21:53:25</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:34</t>
+          <t>2026-10-20 21:53:25</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:34</t>
+          <t>2026-10-20 21:53:25</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:34</t>
+          <t>2026-10-20 21:53:25</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:34</t>
+          <t>2026-10-20 21:53:25</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:34</t>
+          <t>2026-10-20 21:53:25</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:34</t>
+          <t>2026-10-20 21:53:25</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:34</t>
+          <t>2026-10-20 21:53:25</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:35</t>
+          <t>2026-10-20 21:53:26</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:35</t>
+          <t>2026-10-20 21:53:26</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:35</t>
+          <t>2026-10-20 21:53:26</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:35</t>
+          <t>2026-10-20 21:53:26</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-20 21:42:35</t>
+          <t>2026-10-20 21:53:26</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">

--- a/etf_holdings/2026-10-20_00985A_full_holdings.xlsx
+++ b/etf_holdings/2026-10-20_00985A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:22</t>
+          <t>2026-10-20 22:20:05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:22</t>
+          <t>2026-10-20 22:20:05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:22</t>
+          <t>2026-10-20 22:20:05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:22</t>
+          <t>2026-10-20 22:20:05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:22</t>
+          <t>2026-10-20 22:20:05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:22</t>
+          <t>2026-10-20 22:20:05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:22</t>
+          <t>2026-10-20 22:20:05</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:22</t>
+          <t>2026-10-20 22:20:05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:22</t>
+          <t>2026-10-20 22:20:05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:22</t>
+          <t>2026-10-20 22:20:05</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:22</t>
+          <t>2026-10-20 22:20:05</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:22</t>
+          <t>2026-10-20 22:20:05</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:22</t>
+          <t>2026-10-20 22:20:05</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:22</t>
+          <t>2026-10-20 22:20:05</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:22</t>
+          <t>2026-10-20 22:20:05</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:24</t>
+          <t>2026-10-20 22:20:06</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:24</t>
+          <t>2026-10-20 22:20:06</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:24</t>
+          <t>2026-10-20 22:20:06</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:24</t>
+          <t>2026-10-20 22:20:06</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:24</t>
+          <t>2026-10-20 22:20:06</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:24</t>
+          <t>2026-10-20 22:20:06</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:24</t>
+          <t>2026-10-20 22:20:06</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:24</t>
+          <t>2026-10-20 22:20:06</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:24</t>
+          <t>2026-10-20 22:20:06</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:24</t>
+          <t>2026-10-20 22:20:06</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:24</t>
+          <t>2026-10-20 22:20:06</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:24</t>
+          <t>2026-10-20 22:20:06</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:24</t>
+          <t>2026-10-20 22:20:06</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:24</t>
+          <t>2026-10-20 22:20:06</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:24</t>
+          <t>2026-10-20 22:20:06</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:25</t>
+          <t>2026-10-20 22:20:07</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:25</t>
+          <t>2026-10-20 22:20:07</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:25</t>
+          <t>2026-10-20 22:20:07</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:25</t>
+          <t>2026-10-20 22:20:07</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:25</t>
+          <t>2026-10-20 22:20:07</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:25</t>
+          <t>2026-10-20 22:20:07</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:25</t>
+          <t>2026-10-20 22:20:07</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:25</t>
+          <t>2026-10-20 22:20:07</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:25</t>
+          <t>2026-10-20 22:20:07</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:25</t>
+          <t>2026-10-20 22:20:07</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:25</t>
+          <t>2026-10-20 22:20:07</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:25</t>
+          <t>2026-10-20 22:20:07</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:25</t>
+          <t>2026-10-20 22:20:07</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:25</t>
+          <t>2026-10-20 22:20:07</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:25</t>
+          <t>2026-10-20 22:20:07</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:26</t>
+          <t>2026-10-20 22:20:09</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:26</t>
+          <t>2026-10-20 22:20:09</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:26</t>
+          <t>2026-10-20 22:20:09</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:26</t>
+          <t>2026-10-20 22:20:09</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-10-20 21:53:26</t>
+          <t>2026-10-20 22:20:09</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
